--- a/data/trans_dic/P33_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,32; 88,63</t>
+          <t>83,39; 88,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,79; 75,43</t>
+          <t>68,55; 75,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,29; 81,92</t>
+          <t>75,54; 82,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,57; 81,31</t>
+          <t>74,63; 81,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,91; 83,85</t>
+          <t>77,78; 83,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,08; 70,38</t>
+          <t>63,41; 70,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,15; 72,49</t>
+          <t>65,2; 72,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,97; 69,45</t>
+          <t>64,04; 69,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,52; 85,45</t>
+          <t>81,43; 85,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,01; 72,1</t>
+          <t>66,83; 71,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,54; 76,41</t>
+          <t>71,33; 76,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,05; 74,47</t>
+          <t>70,25; 74,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,96; 81,68</t>
+          <t>76,56; 82,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,71; 76,54</t>
+          <t>70,84; 76,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,11; 83,18</t>
+          <t>77,77; 82,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,71; 91,69</t>
+          <t>77,79; 92,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,13; 78,74</t>
+          <t>72,95; 78,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,75; 68,63</t>
+          <t>63,01; 69,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,59; 75,56</t>
+          <t>69,75; 75,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,94; 75,75</t>
+          <t>70,93; 75,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75,53; 79,61</t>
+          <t>75,31; 79,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,62; 71,91</t>
+          <t>67,43; 71,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,81; 78,53</t>
+          <t>74,61; 78,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,27; 85,57</t>
+          <t>75,26; 85,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,93; 83,04</t>
+          <t>76,48; 82,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,29; 80,68</t>
+          <t>73,82; 80,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,35; 77,39</t>
+          <t>70,37; 77,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,4; 76,24</t>
+          <t>68,39; 75,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,08; 73,02</t>
+          <t>66,17; 73,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,11; 73,7</t>
+          <t>67,29; 73,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,74; 72,43</t>
+          <t>66,05; 72,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 72,22</t>
+          <t>30,6; 71,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,48; 77,25</t>
+          <t>72,58; 77,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,63; 76,31</t>
+          <t>71,67; 76,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,28; 73,88</t>
+          <t>69,22; 73,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,53; 72,23</t>
+          <t>38,81; 72,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,91; 83,84</t>
+          <t>78,5; 83,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,89; 76,03</t>
+          <t>69,99; 75,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,78; 76,36</t>
+          <t>70,71; 76,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,39; 74,61</t>
+          <t>68,48; 74,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,15; 79,28</t>
+          <t>74,05; 79,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,23; 69,97</t>
+          <t>64,33; 70,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,7; 76,45</t>
+          <t>70,3; 76,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,47; 75,3</t>
+          <t>65,55; 74,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,94; 80,71</t>
+          <t>77,13; 80,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 71,99</t>
+          <t>67,92; 72,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,38; 75,42</t>
+          <t>71,49; 75,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,86; 73,54</t>
+          <t>67,88; 73,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,16; 82,8</t>
+          <t>79,98; 82,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,57; 75,59</t>
+          <t>72,41; 75,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,34; 78,3</t>
+          <t>75,35; 78,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,57; 82,57</t>
+          <t>74,27; 82,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,51; 77,4</t>
+          <t>74,42; 77,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,24</t>
+          <t>65,63; 69,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,14</t>
+          <t>69,9; 73,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,85; 70,67</t>
+          <t>53,22; 70,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77,7; 79,69</t>
+          <t>77,61; 79,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,84</t>
+          <t>69,68; 71,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,05; 75,15</t>
+          <t>72,94; 75,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,96; 74,31</t>
+          <t>64,36; 74,58</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>570792; 607146</t>
+          <t>571241; 607511</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>483210; 529832</t>
+          <t>481461; 529482</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505405; 549939</t>
+          <t>507067; 550679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>463886; 505771</t>
+          <t>464252; 506189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>534181; 574884</t>
+          <t>533258; 575390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>438934; 489769</t>
+          <t>441247; 490721</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>432859; 481653</t>
+          <t>433208; 481863</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>420030; 456038</t>
+          <t>420478; 457747</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1117298; 1171282</t>
+          <t>1116085; 1172147</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>936928; 1008169</t>
+          <t>934431; 1006297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>955580; 1020602</t>
+          <t>952749; 1017561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>895696; 952150</t>
+          <t>898311; 956124</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>721235; 775614</t>
+          <t>726930; 778976</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>718364; 777590</t>
+          <t>719667; 775604</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>796122; 847798</t>
+          <t>792646; 845302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>903748; 1066273</t>
+          <t>904680; 1074856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>703724; 757744</t>
+          <t>701946; 757605</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>647054; 707700</t>
+          <t>649722; 712514</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>724329; 786472</t>
+          <t>725997; 786637</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>652172; 696426</t>
+          <t>652118; 697130</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1444050; 1521934</t>
+          <t>1439701; 1518491</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1384325; 1471986</t>
+          <t>1380295; 1469136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1541014; 1617629</t>
+          <t>1537052; 1615510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1567387; 1781815</t>
+          <t>1567177; 1789983</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>515933; 556852</t>
+          <t>512903; 556284</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>561382; 609637</t>
+          <t>557764; 608382</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534380; 587830</t>
+          <t>534531; 585550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>441932; 492580</t>
+          <t>441860; 490489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>447687; 494765</t>
+          <t>448351; 496263</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>520865; 572091</t>
+          <t>522266; 573827</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>515456; 567935</t>
+          <t>517904; 569613</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>221537; 645226</t>
+          <t>273342; 642225</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>977099; 1041495</t>
+          <t>978458; 1040524</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1097217; 1168881</t>
+          <t>1097831; 1168645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1069362; 1140442</t>
+          <t>1068561; 1140714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>608575; 1111921</t>
+          <t>597524; 1115040</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>729422; 775001</t>
+          <t>725693; 773764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>656713; 714323</t>
+          <t>657622; 713454</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>663580; 715942</t>
+          <t>662974; 716948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>633173; 690765</t>
+          <t>633992; 692780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>765049; 817914</t>
+          <t>763987; 818790</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>671691; 731714</t>
+          <t>672749; 733412</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>735752; 795557</t>
+          <t>731606; 791465</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>713118; 820177</t>
+          <t>713971; 812004</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1505025; 1578705</t>
+          <t>1508754; 1578864</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1345434; 1429197</t>
+          <t>1348374; 1432030</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1411995; 1492077</t>
+          <t>1414247; 1491979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1367407; 1481878</t>
+          <t>1367775; 1486057</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2588708; 2674029</t>
+          <t>2582930; 2674378</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2477335; 2580460</t>
+          <t>2471615; 2581173</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2552237; 2652505</t>
+          <t>2552675; 2658807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2503236; 2771638</t>
+          <t>2493003; 2764034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2501367; 2598566</t>
+          <t>2498276; 2596209</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2340558; 2457196</t>
+          <t>2329295; 2449801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2468587; 2581803</t>
+          <t>2467351; 2578401</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1916101; 2514675</t>
+          <t>1893941; 2510660</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5118185; 5248700</t>
+          <t>5112156; 5243770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4842118; 5001553</t>
+          <t>4851463; 5009745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5053561; 5198847</t>
+          <t>5045986; 5198786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4492493; 5138820</t>
+          <t>4450941; 5157772</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P33_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,39; 88,68</t>
+          <t>83,7; 88,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,55; 75,38</t>
+          <t>68,92; 75,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,54; 82,03</t>
+          <t>75,41; 81,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,63; 81,38</t>
+          <t>73,9; 80,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,78; 83,92</t>
+          <t>77,88; 83,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,41; 70,52</t>
+          <t>63,36; 70,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,2; 72,52</t>
+          <t>65,65; 72,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64,04; 69,71</t>
+          <t>64,65; 70,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,52</t>
+          <t>81,69; 85,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,83; 71,97</t>
+          <t>67,02; 71,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,33; 76,18</t>
+          <t>71,5; 76,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,25; 74,78</t>
+          <t>70,07; 74,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,56; 82,04</t>
+          <t>76,45; 82,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,84; 76,34</t>
+          <t>70,8; 76,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,77; 82,94</t>
+          <t>77,93; 83,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,79; 92,43</t>
+          <t>76,84; 82,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,95; 78,73</t>
+          <t>72,87; 78,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,01; 69,1</t>
+          <t>62,76; 68,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,75; 75,58</t>
+          <t>69,85; 75,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,93; 75,83</t>
+          <t>71,19; 75,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75,31; 79,43</t>
+          <t>75,52; 79,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,43; 71,77</t>
+          <t>67,37; 71,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,61; 78,42</t>
+          <t>74,46; 78,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,26; 85,96</t>
+          <t>74,89; 78,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,48; 82,95</t>
+          <t>76,79; 83,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,82; 80,51</t>
+          <t>74,05; 80,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,37; 77,09</t>
+          <t>70,36; 77,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,39; 75,92</t>
+          <t>69,07; 76,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,17; 73,25</t>
+          <t>65,91; 72,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,29; 73,93</t>
+          <t>67,11; 73,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,05; 72,65</t>
+          <t>65,43; 72,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,6; 71,89</t>
+          <t>66,86; 72,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,58; 77,18</t>
+          <t>72,38; 77,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,67; 76,29</t>
+          <t>71,62; 76,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,22; 73,9</t>
+          <t>69,02; 73,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,81; 72,43</t>
+          <t>68,86; 73,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,5; 83,7</t>
+          <t>78,69; 83,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,99; 75,93</t>
+          <t>70,09; 76,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,71; 76,47</t>
+          <t>70,39; 76,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,48; 74,83</t>
+          <t>68,89; 74,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,05; 79,36</t>
+          <t>73,87; 79,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,33; 70,13</t>
+          <t>64,33; 69,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,3; 76,05</t>
+          <t>70,4; 76,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,55; 74,55</t>
+          <t>63,38; 68,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,13; 80,71</t>
+          <t>76,99; 80,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,92; 72,13</t>
+          <t>67,94; 72,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,49; 75,42</t>
+          <t>71,49; 75,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,88; 73,75</t>
+          <t>66,99; 70,8</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,98; 82,81</t>
+          <t>79,88; 82,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,41; 75,62</t>
+          <t>72,61; 75,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,35; 78,49</t>
+          <t>75,25; 78,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,27; 82,34</t>
+          <t>73,92; 77,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,42; 77,33</t>
+          <t>74,35; 77,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,63; 69,03</t>
+          <t>65,73; 69,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,9; 73,04</t>
+          <t>69,91; 73,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,22; 70,55</t>
+          <t>67,72; 70,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77,61; 79,61</t>
+          <t>77,7; 79,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,68; 71,95</t>
+          <t>69,55; 71,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,94; 75,15</t>
+          <t>72,96; 75,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,36; 74,58</t>
+          <t>71,3; 73,35</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486818</t>
+          <t>524808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>439024</t>
+          <t>480474</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>925842</t>
+          <t>1005283</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>571241; 607511</t>
+          <t>573345; 608861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>481461; 529482</t>
+          <t>484066; 530111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>507067; 550679</t>
+          <t>506189; 549304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>464252; 506189</t>
+          <t>499783; 545685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>533258; 575390</t>
+          <t>533961; 574603</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>441247; 490721</t>
+          <t>440892; 491970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>433208; 481863</t>
+          <t>436242; 482128</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>420478; 457747</t>
+          <t>460904; 498987</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1116085; 1172147</t>
+          <t>1119681; 1172812</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>934431; 1006297</t>
+          <t>937167; 1006040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>952749; 1017561</t>
+          <t>955100; 1018992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>898311; 956124</t>
+          <t>973362; 1034562</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>965770</t>
+          <t>811792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>673534</t>
+          <t>758917</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1639304</t>
+          <t>1570709</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>726930; 778976</t>
+          <t>725902; 779770</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>719667; 775604</t>
+          <t>719253; 778751</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>792646; 845302</t>
+          <t>794264; 846173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>904680; 1074856</t>
+          <t>784923; 839618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>701946; 757605</t>
+          <t>701189; 756296</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>649722; 712514</t>
+          <t>647142; 711078</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>725997; 786637</t>
+          <t>726984; 787144</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>652118; 697130</t>
+          <t>732972; 780245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1439701; 1518491</t>
+          <t>1443766; 1515709</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1380295; 1469136</t>
+          <t>1379132; 1468512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1537052; 1615510</t>
+          <t>1533950; 1615246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1567177; 1789983</t>
+          <t>1535995; 1607558</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466464</t>
+          <t>539227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>535189</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>953384</t>
+          <t>1074417</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>512903; 556284</t>
+          <t>515003; 556950</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>557764; 608382</t>
+          <t>559556; 610516</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534531; 585550</t>
+          <t>534420; 584901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>441860; 490489</t>
+          <t>512152; 565852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>448351; 496263</t>
+          <t>446575; 494404</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>522266; 573827</t>
+          <t>520901; 573207</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>517904; 569613</t>
+          <t>512983; 570315</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>273342; 642225</t>
+          <t>513510; 558355</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>978458; 1040524</t>
+          <t>975837; 1038432</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1097831; 1168645</t>
+          <t>1097092; 1169431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1068561; 1140714</t>
+          <t>1065337; 1139734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>597524; 1115040</t>
+          <t>1039316; 1114011</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>663126</t>
+          <t>712410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>747977</t>
+          <t>735948</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1411102</t>
+          <t>1448358</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>725693; 773764</t>
+          <t>727418; 773546</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>657622; 713454</t>
+          <t>658558; 715256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>662974; 716948</t>
+          <t>659921; 716424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>633992; 692780</t>
+          <t>681417; 740390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>763987; 818790</t>
+          <t>762173; 817598</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>672749; 733412</t>
+          <t>672767; 729990</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>731606; 791465</t>
+          <t>732636; 792832</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>713971; 812004</t>
+          <t>705542; 761771</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1508754; 1578864</t>
+          <t>1505939; 1577937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1348374; 1432030</t>
+          <t>1348933; 1430068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1414247; 1491979</t>
+          <t>1414249; 1496804</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1367775; 1486057</t>
+          <t>1408390; 1488439</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2582930; 2674378</t>
+          <t>2579842; 2675558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2471615; 2581173</t>
+          <t>2478624; 2587028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2552675; 2658807</t>
+          <t>2549311; 2652481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2493003; 2764034</t>
+          <t>2534456; 2641203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2498276; 2596209</t>
+          <t>2496057; 2595772</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2329295; 2449801</t>
+          <t>2332575; 2454347</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2467351; 2578401</t>
+          <t>2467735; 2577470</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1893941; 2510660</t>
+          <t>2453912; 2557005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5112156; 5243770</t>
+          <t>5117800; 5248057</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4851463; 5009745</t>
+          <t>4842440; 4994265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5045986; 5198786</t>
+          <t>5046798; 5201128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4450941; 5157772</t>
+          <t>5028185; 5172690</t>
         </is>
       </c>
     </row>
